--- a/Wio_BG770A/current/PowerConsumption.xlsx
+++ b/Wio_BG770A/current/PowerConsumption.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takashi\Documents\Arduino\libraries\wio_cellular\wiki\current\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takashi\Documents\Repo\Wiki\Wio_BG770A\current\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777E66F9-AFEF-44F6-AAC7-94DF533027A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D13FAD3-6030-4428-AFF6-E840CCEE7684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{28402467-467B-4468-91F3-9AB095850708}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{28402467-467B-4468-91F3-9AB095850708}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -602,13 +602,13 @@
                 <c:formatCode>#,##0.0;[Red]\-#,##0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.337906879598985</c:v>
+                  <c:v>3.6136838160501097</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5094949922336474</c:v>
+                  <c:v>3.7265709106635132</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.5274033664877127</c:v>
+                  <c:v>3.7382487458406213</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -739,13 +739,13 @@
                 <c:formatCode>#,##0.0;[Red]\-#,##0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>22.485579248508625</c:v>
+                  <c:v>19.56482609478245</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>124.50815436182808</c:v>
+                  <c:v>109.4648143598376</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>227.92189538722664</c:v>
+                  <c:v>202.52435355351477</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1044,6 +1044,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1051,7 +1052,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2143,22 +2143,22 @@
         <v>66</v>
       </c>
       <c r="L4" s="1">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M4" s="1">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="N4" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O4" s="1">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P4" s="1">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="Q4" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.4">
@@ -2193,22 +2193,22 @@
         <v>265</v>
       </c>
       <c r="L5" s="1">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M5" s="1">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="N5" s="1">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="O5" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>5</v>
+        <v>0.317</v>
       </c>
       <c r="Q5" s="1">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.4">
@@ -2243,22 +2243,22 @@
         <v>49</v>
       </c>
       <c r="L6" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M6" s="1">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N6" s="1">
         <v>32</v>
       </c>
       <c r="O6" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="P6" s="1">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="Q6" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.4">
@@ -2293,10 +2293,10 @@
         <v>252</v>
       </c>
       <c r="L7" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M7" s="1">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1">
         <v>269</v>
@@ -2305,10 +2305,10 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="P7" s="1">
-        <v>5</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="Q7" s="1">
-        <v>252</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.4">
@@ -2343,22 +2343,22 @@
         <v>50</v>
       </c>
       <c r="L8" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M8" s="1">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N8" s="1">
         <v>33</v>
       </c>
       <c r="O8" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P8" s="1">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q8" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.4">
@@ -2393,22 +2393,22 @@
         <v>251</v>
       </c>
       <c r="L9" s="1">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M9" s="1">
-        <v>276</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O9" s="1">
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="P9" s="1">
-        <v>5</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="Q9" s="1">
-        <v>252</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.4">
@@ -2443,22 +2443,22 @@
         <v>49</v>
       </c>
       <c r="L10" s="1">
+        <v>36</v>
+      </c>
+      <c r="M10" s="1">
+        <v>225</v>
+      </c>
+      <c r="N10" s="1">
         <v>32</v>
       </c>
-      <c r="M10" s="1">
-        <v>226</v>
-      </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>33</v>
       </c>
-      <c r="O10" s="1">
-        <v>27</v>
-      </c>
       <c r="P10" s="1">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="Q10" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.4">
@@ -2569,28 +2569,28 @@
         <v>66</v>
       </c>
       <c r="L14" s="4">
-        <f t="shared" ref="L14:P14" si="1">L4</f>
-        <v>32</v>
+        <f t="shared" ref="L14:N14" si="1">L4</f>
+        <v>59</v>
       </c>
       <c r="M14" s="4">
         <f t="shared" si="1"/>
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="N14" s="4">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O14" s="4">
         <f>O4</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P14" s="4">
         <f>P4</f>
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="Q14" s="4">
         <f>Q4</f>
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.4">
@@ -2635,27 +2635,27 @@
       </c>
       <c r="L15" s="4">
         <f t="shared" ref="L15:N15" si="3">AVERAGE(L6,L8,L10)</f>
-        <v>31.666666666666668</v>
+        <v>36</v>
       </c>
       <c r="M15" s="4">
         <f t="shared" si="3"/>
-        <v>230</v>
+        <v>230.33333333333334</v>
       </c>
       <c r="N15" s="4">
         <f t="shared" si="3"/>
-        <v>32.666666666666664</v>
+        <v>32.333333333333336</v>
       </c>
       <c r="O15" s="4">
         <f>AVERAGE(O6,O8,O10)</f>
-        <v>26.666666666666668</v>
+        <v>32</v>
       </c>
       <c r="P15" s="4">
         <f>AVERAGE(P6,P8,P10)</f>
-        <v>252</v>
+        <v>246.66666666666666</v>
       </c>
       <c r="Q15" s="4">
         <f>AVERAGE(Q6,Q8,Q10)</f>
-        <v>49.333333333333336</v>
+        <v>47.333333333333336</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.4">
@@ -2699,28 +2699,28 @@
         <v>256</v>
       </c>
       <c r="L16" s="4">
-        <f t="shared" ref="L16:P16" si="5">AVERAGE(L5,L7,L9)</f>
-        <v>22</v>
+        <f t="shared" ref="L16:N16" si="5">AVERAGE(L5,L7,L9)</f>
+        <v>26.666666666666668</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="5"/>
-        <v>174.33333333333334</v>
+        <v>131.66666666666666</v>
       </c>
       <c r="N16" s="4">
         <f t="shared" si="5"/>
-        <v>271.33333333333331</v>
+        <v>268.33333333333331</v>
       </c>
       <c r="O16" s="3">
         <f>AVERAGE(O5,O7,O9)</f>
-        <v>7.4333333333333321E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="P16" s="4">
         <f>AVERAGE(P5,P7,P9)</f>
-        <v>5</v>
+        <v>0.32466666666666666</v>
       </c>
       <c r="Q16" s="4">
         <f>AVERAGE(Q5,Q7,Q9)</f>
-        <v>256.33333333333331</v>
+        <v>290.33333333333331</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.4">
@@ -2770,11 +2770,11 @@
       </c>
       <c r="G21" s="4">
         <f>L15*N15</f>
-        <v>1034.4444444444443</v>
+        <v>1164</v>
       </c>
       <c r="H21" s="4">
         <f>O15*Q15</f>
-        <v>1315.5555555555557</v>
+        <v>1514.6666666666667</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.4">
@@ -2795,11 +2795,11 @@
       </c>
       <c r="G22" s="4">
         <f>L16*(C19-N15)</f>
-        <v>78481.333333333343</v>
+        <v>95137.777777777781</v>
       </c>
       <c r="H22" s="4">
         <f>O16*(C19-Q15)</f>
-        <v>263.93288888888884</v>
+        <v>262.89733333333334</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.4">
@@ -2820,11 +2820,11 @@
       </c>
       <c r="G23" s="4">
         <f>MAX(M14:M16)</f>
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="H23" s="4">
         <f>MAX(P14:P16)</f>
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.4">
@@ -2874,11 +2874,11 @@
       </c>
       <c r="G27" s="4">
         <f>($L$15*$N$15+($L$16*($C27-$N$15)))*(60*60)/$C27</f>
-        <v>82989.333333333328</v>
+        <v>99621.333333333328</v>
       </c>
       <c r="H27" s="4">
         <f>($O$15*$Q$15+($O$16*($C27-$Q$15)))*(60*60)/$C27</f>
-        <v>16010.261333333334</v>
+        <v>18400.368000000002</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.4">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G28" s="4">
         <f t="shared" ref="G28:G30" si="6">($L$15*$N$15+($L$16*($C28-$N$15)))*(60*60)/$C28</f>
-        <v>80463.111111111124</v>
+        <v>97207.111111111109</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" ref="H28:H30" si="7">($O$15*$Q$15+($O$16*($C28-$Q$15)))*(60*60)/$C28</f>
-        <v>5515.1537777777785</v>
+        <v>6311.0560000000005</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.4">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="G29" s="4">
         <f t="shared" si="6"/>
-        <v>79831.555555555562</v>
+        <v>96603.555555555562</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="7"/>
-        <v>2891.376888888889</v>
+        <v>3288.7280000000001</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.4">
@@ -2961,11 +2961,11 @@
       </c>
       <c r="G30" s="4">
         <f t="shared" si="6"/>
-        <v>79515.777777777781</v>
+        <v>96301.777777777781</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="7"/>
-        <v>1579.4884444444444</v>
+        <v>1777.5640000000001</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.4">
@@ -3023,11 +3023,11 @@
       </c>
       <c r="G34" s="7">
         <f t="shared" si="8"/>
-        <v>4.337906879598985</v>
+        <v>3.6136838160501097</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="8"/>
-        <v>22.485579248508625</v>
+        <v>19.56482609478245</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.4">
@@ -3049,11 +3049,11 @@
       </c>
       <c r="G35" s="7">
         <f t="shared" si="10"/>
-        <v>4.4740999326123214</v>
+        <v>3.703432762120741</v>
       </c>
       <c r="H35" s="7">
         <f t="shared" si="10"/>
-        <v>65.27469849536179</v>
+        <v>57.042751640929822</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.4">
@@ -3075,11 +3075,11 @@
       </c>
       <c r="G36" s="7">
         <f t="shared" si="11"/>
-        <v>4.5094949922336474</v>
+        <v>3.7265709106635132</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" si="11"/>
-        <v>124.50815436182808</v>
+        <v>109.4648143598376</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.4">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="G37" s="7">
         <f t="shared" si="12"/>
-        <v>4.5274033664877127</v>
+        <v>3.7382487458406213</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="12"/>
-        <v>227.92189538722664</v>
+        <v>202.52435355351477</v>
       </c>
     </row>
   </sheetData>
